--- a/Result/profitability/3054.xlsx
+++ b/Result/profitability/3054.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.05</v>
       </c>
       <c r="M2" t="n">
-        <v>0.38625</v>
+        <v>0.60875</v>
       </c>
       <c r="N2" t="n">
-        <v>35.1125</v>
+        <v>37.6675</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.06</v>
       </c>
       <c r="M3" t="n">
-        <v>0.43</v>
+        <v>0.6212500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>34.54875</v>
+        <v>35.81375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.12</v>
       </c>
       <c r="M4" t="n">
-        <v>0.42</v>
+        <v>0.60875</v>
       </c>
       <c r="N4" t="n">
-        <v>32.44375</v>
+        <v>33.83125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.33</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4637500000000001</v>
+        <v>0.6475000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>31.86375</v>
+        <v>33.11375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.26</v>
       </c>
       <c r="M6" t="n">
-        <v>0.49375</v>
+        <v>0.5975</v>
       </c>
       <c r="N6" t="n">
-        <v>29.44</v>
+        <v>32.00125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.28</v>
       </c>
       <c r="M7" t="n">
-        <v>0.44625</v>
+        <v>0.47</v>
       </c>
       <c r="N7" t="n">
-        <v>28.3525</v>
+        <v>25.5175</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.26</v>
       </c>
       <c r="M8" t="n">
-        <v>0.31625</v>
+        <v>0.32625</v>
       </c>
       <c r="N8" t="n">
-        <v>22.1825</v>
+        <v>17.6525</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3054</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>203</v>
+      </c>
+      <c r="D75" t="n">
+        <v>123</v>
+      </c>
+      <c r="E75" t="n">
+        <v>80</v>
+      </c>
+      <c r="F75" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="G75" t="n">
+        <v>56</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>27.53%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>75</v>
+      </c>
+      <c r="J75" t="n">
+        <v>131</v>
+      </c>
+      <c r="K75" t="n">
+        <v>120</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.56625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>37.73625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.05673758865248235</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-36.23999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.4791749305831019</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3402517863218781</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
